--- a/resources/templates/standard/K1100-01.xlsx
+++ b/resources/templates/standard/K1100-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">     PURCHASE ORDER (원자재 입고 요청서)</t>
   </si>
@@ -1478,7 +1481,9 @@
   <sheetData>
     <row r="1" ht="7.5" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1510,7 +1515,7 @@
     <row r="2" ht="31.5" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1605,7 +1610,7 @@
     <row r="5" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
@@ -1638,7 +1643,7 @@
     <row r="6" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
@@ -1671,7 +1676,7 @@
     <row r="7" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
@@ -1682,11 +1687,11 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -1708,7 +1713,7 @@
     <row r="8" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
@@ -1719,11 +1724,11 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1745,7 +1750,7 @@
     <row r="9" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
@@ -1756,11 +1761,11 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -1782,7 +1787,7 @@
     <row r="10" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="7"/>
@@ -1793,11 +1798,11 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
@@ -1819,7 +1824,7 @@
     <row r="11" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="7"/>
@@ -1830,11 +1835,11 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -1849,7 +1854,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -1919,41 +1924,41 @@
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R14" s="11"/>
       <c r="S14" s="3"/>
@@ -1973,26 +1978,26 @@
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L15" s="14"/>
       <c r="M15" s="15"/>
@@ -2018,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="23">
         <v>27.2</v>
@@ -2055,7 +2060,7 @@
         <f>SUM(K16*L16)</f>
       </c>
       <c r="P16" s="31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="32"/>
       <c r="R16" s="32"/>
@@ -2076,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="35">
         <v>27.2</v>
@@ -2113,7 +2118,7 @@
         <f>SUM(K17*L17)</f>
       </c>
       <c r="P17" s="42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q17" s="43"/>
       <c r="R17" s="43"/>
@@ -2132,10 +2137,10 @@
     <row r="18" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
       <c r="B18" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="35">
         <v>27.2</v>
@@ -2184,10 +2189,10 @@
     <row r="19" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
       <c r="B19" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="23">
         <v>27.2</v>
@@ -2236,10 +2241,10 @@
     <row r="20" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="21"/>
       <c r="B20" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
@@ -2280,10 +2285,10 @@
     <row r="21" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="21"/>
       <c r="B21" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
@@ -2324,10 +2329,10 @@
     <row r="22" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="21"/>
       <c r="B22" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
@@ -2368,10 +2373,10 @@
     <row r="23" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="21"/>
       <c r="B23" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
@@ -2412,10 +2417,10 @@
     <row r="24" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="21"/>
       <c r="B24" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="24"/>
@@ -2456,10 +2461,10 @@
     <row r="25" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="21"/>
       <c r="B25" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
@@ -2500,10 +2505,10 @@
     <row r="26" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="21"/>
       <c r="B26" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" s="28"/>
       <c r="E26" s="48"/>
@@ -2527,7 +2532,7 @@
         <f>SUM(K26*L26)</f>
       </c>
       <c r="P26" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q26" s="51"/>
       <c r="R26" s="51"/>
@@ -2546,10 +2551,10 @@
     <row r="27" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="21"/>
       <c r="B27" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" s="28"/>
       <c r="E27" s="48"/>
@@ -2590,10 +2595,10 @@
     <row r="28" ht="30" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="21"/>
       <c r="B28" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="48"/>
@@ -2618,7 +2623,7 @@
       </c>
       <c r="P28" s="31"/>
       <c r="Q28" s="51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="1"/>
@@ -2636,10 +2641,10 @@
     <row r="29" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="21"/>
       <c r="B29" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="28"/>
       <c r="E29" s="48"/>
@@ -2680,10 +2685,10 @@
     <row r="30" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="21"/>
       <c r="B30" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="28"/>
       <c r="E30" s="48"/>
@@ -2707,7 +2712,7 @@
         <f>O18</f>
       </c>
       <c r="P30" s="53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q30" s="54"/>
       <c r="R30" s="54"/>
@@ -2726,10 +2731,10 @@
     <row r="31" ht="26.25" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
       <c r="B31" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D31" s="28"/>
       <c r="E31" s="48"/>
@@ -2753,7 +2758,7 @@
         <f>O18</f>
       </c>
       <c r="P31" s="53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q31" s="54"/>
       <c r="R31" s="54"/>
@@ -2772,10 +2777,10 @@
     <row r="32" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="21"/>
       <c r="B32" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="28"/>
       <c r="E32" s="48"/>
@@ -2800,7 +2805,7 @@
       </c>
       <c r="P32" s="53"/>
       <c r="Q32" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R32" s="54"/>
       <c r="S32" s="1"/>
@@ -2818,10 +2823,10 @@
     <row r="33" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="21"/>
       <c r="B33" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="24"/>
@@ -2862,10 +2867,10 @@
     <row r="34" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="21"/>
       <c r="B34" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="24"/>
@@ -2906,10 +2911,10 @@
     <row r="35" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="21"/>
       <c r="B35" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="24"/>
@@ -2950,10 +2955,10 @@
     <row r="36" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D36" s="58"/>
       <c r="E36" s="59"/>
@@ -2978,7 +2983,7 @@
       </c>
       <c r="P36" s="67"/>
       <c r="Q36" s="68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R36" s="68"/>
       <c r="S36" s="1"/>
@@ -2996,10 +3001,10 @@
     <row r="37" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D37" s="58"/>
       <c r="E37" s="59"/>
@@ -3040,10 +3045,10 @@
     <row r="38" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D38" s="58"/>
       <c r="E38" s="59"/>
@@ -3084,10 +3089,10 @@
     <row r="39" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="56"/>
       <c r="B39" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D39" s="58"/>
       <c r="E39" s="59"/>
@@ -3128,10 +3133,10 @@
     <row r="40" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="56"/>
       <c r="B40" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" s="58"/>
       <c r="E40" s="59"/>
@@ -3172,10 +3177,10 @@
     <row r="41" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="71"/>
       <c r="B41" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="72"/>
       <c r="E41" s="59"/>
@@ -3216,10 +3221,10 @@
     <row r="42" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="56"/>
       <c r="B42" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="58"/>
       <c r="E42" s="59"/>
@@ -3243,10 +3248,10 @@
         <f>O18</f>
       </c>
       <c r="P42" s="69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q42" s="73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R42" s="73"/>
       <c r="S42" s="1"/>
@@ -3264,10 +3269,10 @@
     <row r="43" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="56"/>
       <c r="B43" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D43" s="58"/>
       <c r="E43" s="59"/>
@@ -3308,10 +3313,10 @@
     <row r="44" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="56"/>
       <c r="B44" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D44" s="58"/>
       <c r="E44" s="59"/>
@@ -3352,10 +3357,10 @@
     <row r="45" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="56"/>
       <c r="B45" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D45" s="58"/>
       <c r="E45" s="59"/>
@@ -3396,10 +3401,10 @@
     <row r="46" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="56"/>
       <c r="B46" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46" s="58"/>
       <c r="E46" s="59"/>
@@ -3423,7 +3428,7 @@
         <f>SUM(K46*L46)</f>
       </c>
       <c r="P46" s="69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q46" s="73"/>
       <c r="R46" s="73"/>
@@ -3442,10 +3447,10 @@
     <row r="47" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="71"/>
       <c r="B47" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D47" s="72"/>
       <c r="E47" s="59"/>
@@ -3486,10 +3491,10 @@
     <row r="48" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="71"/>
       <c r="B48" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D48" s="58"/>
       <c r="E48" s="59"/>
@@ -3530,10 +3535,10 @@
     <row r="49" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="71"/>
       <c r="B49" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D49" s="58"/>
       <c r="E49" s="59"/>
@@ -3574,10 +3579,10 @@
     <row r="50" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="71"/>
       <c r="B50" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D50" s="58"/>
       <c r="E50" s="59"/>
@@ -3618,10 +3623,10 @@
     <row r="51" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="71"/>
       <c r="B51" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D51" s="58"/>
       <c r="E51" s="59"/>
@@ -3662,10 +3667,10 @@
     <row r="52" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="71"/>
       <c r="B52" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C52" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D52" s="58"/>
       <c r="E52" s="59"/>
@@ -3706,10 +3711,10 @@
     <row r="53" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="71"/>
       <c r="B53" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D53" s="72"/>
       <c r="E53" s="59"/>
@@ -3733,7 +3738,7 @@
         <f>O18</f>
       </c>
       <c r="P53" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q53" s="70"/>
       <c r="R53" s="70"/>
@@ -3782,22 +3787,22 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y54" s="77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z54" s="77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA54" s="77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB54" s="77" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC54" s="77" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" ht="20.1" customHeight="1" hidden="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -3864,7 +3869,7 @@
         <f>O18</f>
       </c>
       <c r="P56" s="67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q56" s="68"/>
       <c r="R56" s="68"/>
@@ -4178,7 +4183,7 @@
         <f>O18</f>
       </c>
       <c r="P64" s="69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q64" s="79"/>
       <c r="R64" s="79"/>
@@ -4414,7 +4419,7 @@
         <f>O18</f>
       </c>
       <c r="P70" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q70" s="51"/>
       <c r="R70" s="51"/>
@@ -4572,7 +4577,7 @@
         <f>SUM(K74*L74)</f>
       </c>
       <c r="P74" s="31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q74" s="83"/>
       <c r="R74" s="83"/>
@@ -4614,7 +4619,7 @@
       </c>
       <c r="P75" s="31"/>
       <c r="Q75" s="83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R75" s="83"/>
       <c r="S75" s="1"/>
@@ -4687,7 +4692,7 @@
         <f>K16</f>
       </c>
       <c r="L77" s="84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M77" s="84"/>
       <c r="N77" s="84"/>
@@ -4695,10 +4700,10 @@
         <f>O18</f>
       </c>
       <c r="P77" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q77" s="83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R77" s="83"/>
       <c r="S77" s="1"/>
@@ -4732,7 +4737,7 @@
         <f>K16</f>
       </c>
       <c r="L78" s="84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M78" s="84"/>
       <c r="N78" s="84"/>
@@ -4740,10 +4745,10 @@
         <f>O18</f>
       </c>
       <c r="P78" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q78" s="83" t="s">
         <v>57</v>
-      </c>
-      <c r="Q78" s="83" t="s">
-        <v>56</v>
       </c>
       <c r="R78" s="83"/>
       <c r="S78" s="1"/>
@@ -4783,10 +4788,10 @@
         <f>O18</f>
       </c>
       <c r="P79" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q79" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R79" s="85"/>
       <c r="S79" s="1"/>
@@ -4820,7 +4825,7 @@
         <f t="shared" ref="K80:K108" si="7">SUM(G80*F80*J80)</f>
       </c>
       <c r="L80" s="84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M80" s="84"/>
       <c r="N80" s="84"/>
@@ -4828,10 +4833,10 @@
         <f>O18</f>
       </c>
       <c r="P80" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q80" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R80" s="51"/>
       <c r="S80" s="1"/>
@@ -4839,7 +4844,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X80" s="76"/>
       <c r="Y80" s="78"/>
@@ -4867,7 +4872,7 @@
         <f>SUM(G81*F81*J81)</f>
       </c>
       <c r="L81" s="84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M81" s="84"/>
       <c r="N81" s="84"/>
@@ -4875,7 +4880,7 @@
         <f>SUM(K81*L81)</f>
       </c>
       <c r="P81" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q81" s="51"/>
       <c r="R81" s="51"/>
@@ -4916,10 +4921,10 @@
         <f>O18</f>
       </c>
       <c r="P82" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q82" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R82" s="51"/>
       <c r="S82" s="1"/>
@@ -4953,7 +4958,7 @@
         <f>K80</f>
       </c>
       <c r="L83" s="84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M83" s="84"/>
       <c r="N83" s="84"/>
@@ -4961,7 +4966,7 @@
         <f>O18</f>
       </c>
       <c r="P83" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q83" s="51"/>
       <c r="R83" s="51"/>
@@ -4996,7 +5001,7 @@
         <f>SUM(G84*F84*J84)</f>
       </c>
       <c r="L84" s="84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M84" s="84"/>
       <c r="N84" s="84"/>
@@ -5004,10 +5009,10 @@
         <f>SUM(K84*L84)</f>
       </c>
       <c r="P84" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q84" s="83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R84" s="83"/>
       <c r="S84" s="1"/>
@@ -5047,7 +5052,7 @@
         <f>O18</f>
       </c>
       <c r="P85" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q85" s="83"/>
       <c r="R85" s="83"/>
@@ -5088,7 +5093,7 @@
         <f>O18</f>
       </c>
       <c r="P86" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q86" s="83"/>
       <c r="R86" s="83"/>
@@ -5129,7 +5134,7 @@
         <f>O18</f>
       </c>
       <c r="P87" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q87" s="83"/>
       <c r="R87" s="83"/>
@@ -5170,7 +5175,7 @@
         <f>O18</f>
       </c>
       <c r="P88" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q88" s="83"/>
       <c r="R88" s="83"/>
@@ -5211,7 +5216,7 @@
         <f>O18</f>
       </c>
       <c r="P89" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q89" s="83"/>
       <c r="R89" s="83"/>
@@ -5252,7 +5257,7 @@
         <f>O18</f>
       </c>
       <c r="P90" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q90" s="83"/>
       <c r="R90" s="83"/>
@@ -5293,7 +5298,7 @@
         <f>O18</f>
       </c>
       <c r="P91" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q91" s="83"/>
       <c r="R91" s="83"/>
@@ -5334,7 +5339,7 @@
         <f>O18</f>
       </c>
       <c r="P92" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q92" s="83"/>
       <c r="R92" s="83"/>
@@ -5369,7 +5374,7 @@
         <f>K80</f>
       </c>
       <c r="L93" s="84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M93" s="84"/>
       <c r="N93" s="84"/>
@@ -5377,7 +5382,7 @@
         <f>O18</f>
       </c>
       <c r="P93" s="31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q93" s="83"/>
       <c r="R93" s="83"/>
@@ -5412,7 +5417,7 @@
         <f>K80</f>
       </c>
       <c r="L94" s="84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M94" s="84"/>
       <c r="N94" s="84"/>
@@ -5420,10 +5425,10 @@
         <f t="shared" ref="O94:O107" si="8">SUM(K94*L94)</f>
       </c>
       <c r="P94" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q94" s="51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R94" s="51"/>
       <c r="S94" s="7"/>
@@ -5457,7 +5462,7 @@
         <f>K80</f>
       </c>
       <c r="L95" s="84" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M95" s="84"/>
       <c r="N95" s="84"/>
@@ -5465,7 +5470,7 @@
         <f>O94</f>
       </c>
       <c r="P95" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q95" s="83"/>
       <c r="R95" s="83"/>
@@ -5500,7 +5505,7 @@
         <f>K80</f>
       </c>
       <c r="L96" s="84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M96" s="84"/>
       <c r="N96" s="84"/>
@@ -5508,10 +5513,10 @@
         <f>O94</f>
       </c>
       <c r="P96" s="92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q96" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R96" s="85"/>
       <c r="S96" s="7"/>
@@ -5707,7 +5712,7 @@
         <f>O94</f>
       </c>
       <c r="P101" s="92" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q101" s="85"/>
       <c r="R101" s="85"/>
@@ -5787,7 +5792,7 @@
         <f>O94</f>
       </c>
       <c r="P103" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q103" s="85"/>
       <c r="R103" s="85"/>
@@ -5828,7 +5833,7 @@
         <f>O94</f>
       </c>
       <c r="P104" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q104" s="85"/>
       <c r="R104" s="85"/>
@@ -5947,7 +5952,7 @@
         <f>O94</f>
       </c>
       <c r="P107" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q107" s="45"/>
       <c r="R107" s="45"/>
@@ -6004,7 +6009,7 @@
     </row>
     <row r="109" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -6201,7 +6206,7 @@
     <row r="115" ht="15.75" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="115"/>
       <c r="B115" s="121" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C115" s="116"/>
       <c r="D115" s="116"/>
@@ -6234,7 +6239,7 @@
     <row r="116" ht="23.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="115"/>
       <c r="B116" s="122" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C116" s="122"/>
       <c r="D116" s="122"/>
@@ -6267,7 +6272,7 @@
     <row r="117" ht="21.75" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="115"/>
       <c r="B117" s="122" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C117" s="122"/>
       <c r="D117" s="122"/>
@@ -6300,7 +6305,7 @@
     <row r="118" ht="20.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="115"/>
       <c r="B118" s="122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C118" s="122"/>
       <c r="D118" s="122"/>
@@ -6363,7 +6368,7 @@
     </row>
     <row r="120" ht="10.5" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="115" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B120" s="116"/>
       <c r="C120" s="116"/>
@@ -6397,7 +6402,7 @@
     <row r="121" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="125"/>
       <c r="B121" s="121" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -6432,7 +6437,7 @@
     <row r="122" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="125"/>
       <c r="B122" s="122" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -6467,7 +6472,7 @@
     <row r="123" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="125"/>
       <c r="B123" s="122" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -6502,7 +6507,7 @@
     <row r="124" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="125"/>
       <c r="B124" s="122" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -6537,7 +6542,7 @@
     <row r="125" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="125"/>
       <c r="B125" s="122" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -6572,7 +6577,7 @@
     <row r="126" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="125"/>
       <c r="B126" s="122" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -6605,7 +6610,7 @@
     <row r="127" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="125"/>
       <c r="B127" s="122" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
